--- a/data/trending_integrated_20261007_15.xlsx
+++ b/data/trending_integrated_20261007_15.xlsx
@@ -578,10 +578,10 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2" t="n">
         <v>52</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26427552984</v>
+        <v>26447328504</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -655,79 +655,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>국전</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11220</v>
+        <v>2755</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.03%</t>
+          <t>'+15.03%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.17</v>
+        <v>0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="F3" t="n">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>515</v>
+        <v>122</v>
       </c>
       <c r="H3" t="n">
-        <v>5.01</v>
+        <v>1.36</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9670</v>
+        <v>2395</v>
       </c>
       <c r="K3" t="n">
-        <v>11020</v>
+        <v>2410</v>
       </c>
       <c r="L3" t="n">
-        <v>11250</v>
+        <v>3020</v>
       </c>
       <c r="M3" t="n">
-        <v>10300</v>
+        <v>2405</v>
       </c>
       <c r="N3" t="n">
-        <v>4.84</v>
+        <v>1.31</v>
       </c>
       <c r="O3" t="n">
-        <v>30625078170</v>
+        <v>41288100015</v>
       </c>
       <c r="P3" t="n">
-        <v>15900</v>
+        <v>6000</v>
       </c>
       <c r="Q3" t="n">
-        <v>6310</v>
+        <v>1700</v>
       </c>
       <c r="R3" t="n">
-        <v>-105000</v>
+        <v>-120000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>러시아 흑사병, 케냐 에볼라 등 전염병 확산 관련 뉴스가 부각되며 테마주로 언급. 일부는 급등 기대를 보이나, 사실 관계 확인이 필요.</t>
+          <t>흑사병 테마 관련주로 언급되며 거래량은 터졌으나 큰 상승은 못함. 반도체/이차전지 소재 업체로 변신 시도 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['흑사병', '에볼라', '테마주']</t>
+          <t>['흑사병', '테마주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>307750</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>국전</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2775</v>
+        <v>7755</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.87%</t>
+          <t>'+14.89%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>92</v>
+        <v>171</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="G4" t="n">
-        <v>108</v>
+        <v>548</v>
       </c>
       <c r="H4" t="n">
-        <v>1.36</v>
+        <v>5.12</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2395</v>
+        <v>6750</v>
       </c>
       <c r="K4" t="n">
-        <v>2410</v>
+        <v>6710</v>
       </c>
       <c r="L4" t="n">
-        <v>3020</v>
+        <v>8450</v>
       </c>
       <c r="M4" t="n">
-        <v>2405</v>
+        <v>6690</v>
       </c>
       <c r="N4" t="n">
-        <v>1.31</v>
+        <v>5.14</v>
       </c>
       <c r="O4" t="n">
-        <v>40816646232</v>
+        <v>141547431725</v>
       </c>
       <c r="P4" t="n">
-        <v>6000</v>
+        <v>23500</v>
       </c>
       <c r="Q4" t="n">
-        <v>1700</v>
+        <v>2890</v>
       </c>
       <c r="R4" t="n">
-        <v>-120000</v>
+        <v>-631000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>흑사병 테마 관련주로 언급되며 거래량은 터졌으나 큰 상승은 못함. 반도체/이차전지 소재 업체로 변신 시도 언급.</t>
+          <t>정부의 용적률 상향 및 그린벨트 해제 발표와 함께 성수동 삼표타워 건설 시작. 만원 돌파 기대감 및 거래량 증가.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['흑사병', '테마주']</t>
+          <t>['용적률', '그린벨트', '거래량']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,82 +827,82 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>307750</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7780</v>
+        <v>11010</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.26%</t>
+          <t>'+13.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>0.17</v>
       </c>
       <c r="E5" t="n">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="F5" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G5" t="n">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="H5" t="n">
-        <v>5.12</v>
+        <v>5.01</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6750</v>
+        <v>9670</v>
       </c>
       <c r="K5" t="n">
-        <v>6710</v>
+        <v>11020</v>
       </c>
       <c r="L5" t="n">
-        <v>8450</v>
+        <v>11250</v>
       </c>
       <c r="M5" t="n">
-        <v>6690</v>
+        <v>10300</v>
       </c>
       <c r="N5" t="n">
-        <v>5.14</v>
+        <v>4.84</v>
       </c>
       <c r="O5" t="n">
-        <v>140394898230</v>
+        <v>31997231395</v>
       </c>
       <c r="P5" t="n">
-        <v>23500</v>
+        <v>15900</v>
       </c>
       <c r="Q5" t="n">
-        <v>2890</v>
+        <v>6310</v>
       </c>
       <c r="R5" t="n">
-        <v>-631000</v>
+        <v>-105000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정부의 용적률 상향 및 그린벨트 해제 발표와 함께 성수동 삼표타워 건설 시작. 만원 돌파 기대감 및 거래량 증가.</t>
+          <t>러시아 흑사병 사망자 발생 소식에 신풍제약이 테마주로 부각되며 급등, 과거 코로나 시절의 경험을 바탕으로 기대감이 형성되고 있음.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['용적률', '그린벨트', '거래량']</t>
+          <t>['흑사병', '테마주', '급등']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16710</v>
+        <v>25600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.37%</t>
+          <t>'+11.55%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.98</v>
+        <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="F6" t="n">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>339</v>
+        <v>304</v>
       </c>
       <c r="H6" t="n">
-        <v>2.37</v>
+        <v>2.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14870</v>
+        <v>22950</v>
       </c>
       <c r="K6" t="n">
-        <v>15480</v>
+        <v>26200</v>
       </c>
       <c r="L6" t="n">
-        <v>17590</v>
+        <v>27600</v>
       </c>
       <c r="M6" t="n">
-        <v>14600</v>
+        <v>25550</v>
       </c>
       <c r="N6" t="n">
-        <v>1.39</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>290508644745</v>
+        <v>104902500825</v>
       </c>
       <c r="P6" t="n">
-        <v>17590</v>
+        <v>30100</v>
       </c>
       <c r="Q6" t="n">
-        <v>6320</v>
+        <v>11140</v>
       </c>
       <c r="R6" t="n">
-        <v>-95000</v>
+        <v>160000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-227000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>국내외 해킹·보안 이슈 부각 속 라온시큐어 상승. 농협·KDB생명 해킹 방어 및 양자보안 공급 논의.</t>
+          <t>유리 기술력 기반 성장 기대감. 브로드컴, 씨게이트 등 대기업과의 협력 가능성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['양자보안', '해킹', '보안주']</t>
+          <t>['유리', '기술력', '협력']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25750</v>
+        <v>13750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+12.20%</t>
+          <t>'+11.52%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="G7" t="n">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="H7" t="n">
-        <v>2.82</v>
+        <v>0.79</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>22950</v>
+        <v>12330</v>
       </c>
       <c r="K7" t="n">
-        <v>26200</v>
+        <v>12580</v>
       </c>
       <c r="L7" t="n">
-        <v>27600</v>
+        <v>14260</v>
       </c>
       <c r="M7" t="n">
-        <v>25550</v>
+        <v>12300</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>0.48</v>
       </c>
       <c r="O7" t="n">
-        <v>103907360925</v>
+        <v>228577797640</v>
       </c>
       <c r="P7" t="n">
-        <v>30100</v>
+        <v>20850</v>
       </c>
       <c r="Q7" t="n">
-        <v>11140</v>
+        <v>4020</v>
       </c>
       <c r="R7" t="n">
-        <v>160000</v>
+        <v>-68000</v>
       </c>
       <c r="S7" t="n">
-        <v>-227000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유리 기술력 기반 성장 기대감. 브로드컴, 씨게이트 등 대기업과의 협력 가능성.</t>
+          <t>한화파워향 가스터빈 블레이드 첫 납품 뉴스가 나왔으나, 주포의 이탈 및 일부 투자자들의 부정적 전망과 함께 변동성이 큰 하루를 보임.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유리', '기술력', '협력']</t>
+          <t>['가스터빈', '납품', '뉴스']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,43 +1103,43 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13630</v>
+        <v>16570</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+10.54%</t>
+          <t>'+11.43%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.31</v>
+        <v>0.98</v>
       </c>
       <c r="E8" t="n">
-        <v>125</v>
+        <v>204</v>
       </c>
       <c r="F8" t="n">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="G8" t="n">
-        <v>247</v>
+        <v>345</v>
       </c>
       <c r="H8" t="n">
-        <v>0.79</v>
+        <v>2.37</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12330</v>
+        <v>14870</v>
       </c>
       <c r="K8" t="n">
-        <v>12580</v>
+        <v>15480</v>
       </c>
       <c r="L8" t="n">
-        <v>14260</v>
+        <v>17590</v>
       </c>
       <c r="M8" t="n">
-        <v>12300</v>
+        <v>14600</v>
       </c>
       <c r="N8" t="n">
-        <v>0.48</v>
+        <v>1.39</v>
       </c>
       <c r="O8" t="n">
-        <v>220926540005</v>
+        <v>293227829885</v>
       </c>
       <c r="P8" t="n">
-        <v>20850</v>
+        <v>17590</v>
       </c>
       <c r="Q8" t="n">
-        <v>4020</v>
+        <v>6320</v>
       </c>
       <c r="R8" t="n">
-        <v>-68000</v>
+        <v>-95000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>한화파워향 가스터빈 블레이드 첫 납품 뉴스에 따른 상승 기대감과 함께, 원자력 발전 투자 가능성 언급. 주포 이탈 및 개미 털기 논란.</t>
+          <t>국내외 해킹·보안 이슈 부각 속 라온시큐어 상승. 농협·KDB생명 해킹 방어 및 양자보안 공급 논의.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['가스터빈', '납품', '원자력']</t>
+          <t>['양자보안', '해킹', '보안주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2610</v>
+        <v>2600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+9.43%</t>
+          <t>'+9.01%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.29</v>
       </c>
       <c r="E9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H9" t="n">
         <v>0.82</v>
@@ -1254,7 +1254,7 @@
         <v>1.11</v>
       </c>
       <c r="O9" t="n">
-        <v>15348850405</v>
+        <v>15490884448</v>
       </c>
       <c r="P9" t="n">
         <v>4760</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5240</v>
+        <v>5200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.59%</t>
+          <t>'+3.79%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>3.32</v>
       </c>
       <c r="E10" t="n">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F10" t="n">
         <v>114</v>
       </c>
       <c r="G10" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="H10" t="n">
         <v>4.72</v>
@@ -1346,7 +1346,7 @@
         <v>1.4</v>
       </c>
       <c r="O10" t="n">
-        <v>241219843520</v>
+        <v>243439565595</v>
       </c>
       <c r="P10" t="n">
         <v>8100</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시 강세 및 2200억원 규모 선주문 관련 언급이 있으나, 투자자들의 불안감도 공존함.</t>
+          <t>미국 증시 호조와 더불어 엠바고 해제 시 2200억 규모의 선주문 발주서 기준 물량에 대한 기대감으로 상승 가능성이 언급되고 있으나, 일부 투자자는 물려있는 상황.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['선주문', '미국 증시', '물량']</t>
+          <t>['선주문', '발주서', '미국 증시']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>244500</v>
+        <v>243500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.45%</t>
+          <t>'+1.04%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.04</v>
       </c>
       <c r="E11" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F11" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G11" t="n">
-        <v>1238</v>
+        <v>1249</v>
       </c>
       <c r="H11" t="n">
         <v>4.12</v>
@@ -1438,7 +1438,7 @@
         <v>4.08</v>
       </c>
       <c r="O11" t="n">
-        <v>102606950750</v>
+        <v>105155064500</v>
       </c>
       <c r="P11" t="n">
         <v>1233000</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6985</v>
+        <v>6980</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>59</v>
       </c>
       <c r="G12" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="H12" t="n">
         <v>1.1</v>
@@ -1530,7 +1530,7 @@
         <v>1.87</v>
       </c>
       <c r="O12" t="n">
-        <v>70969911880</v>
+        <v>72889559255</v>
       </c>
       <c r="P12" t="n">
         <v>11370</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>270500</v>
+        <v>269000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.55%</t>
+          <t>'-1.10%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="G13" t="n">
-        <v>1251</v>
+        <v>1297</v>
       </c>
       <c r="H13" t="n">
         <v>46.37</v>
@@ -1622,7 +1622,7 @@
         <v>46.41</v>
       </c>
       <c r="O13" t="n">
-        <v>3734639978000</v>
+        <v>3885476579500</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>AMD HBM 주문 및 파운드리 계약 소식이 있으나, 정치적 이슈와 외국인/국내 기관의 매도세가 주가에 부정적 영향을 미치고 있다는 분석.</t>
+          <t>AMD CEO의 HBM 대량 주문 및 파운드리 계약 소식에도 불구하고, 투자자들은 실적 전망 및 외인/국장 매도세에 대한 우려를 표하며 부정적인 전망을 보임.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['HBM', '파운드리', '매도세']</t>
+          <t>['HBM', '파운드리', '실적']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1682,13 +1682,13 @@
         <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="F14" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G14" t="n">
-        <v>895</v>
+        <v>907</v>
       </c>
       <c r="H14" t="n">
         <v>22.59</v>
@@ -1714,7 +1714,7 @@
         <v>22.56</v>
       </c>
       <c r="O14" t="n">
-        <v>164246430050</v>
+        <v>168322636000</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17420</v>
+        <v>17370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.86%</t>
+          <t>'-2.14%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F15" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="H15" t="n">
         <v>9.5</v>
@@ -1800,13 +1800,13 @@
         <v>18030</v>
       </c>
       <c r="M15" t="n">
-        <v>17410</v>
+        <v>17370</v>
       </c>
       <c r="N15" t="n">
         <v>9.390000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>56172205245</v>
+        <v>58389197265</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>46250</v>
+        <v>12700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.43%</t>
+          <t>'-2.38%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.02</v>
+        <v>1.88</v>
       </c>
       <c r="E16" t="n">
-        <v>378</v>
+        <v>92</v>
       </c>
       <c r="F16" t="n">
-        <v>207</v>
+        <v>67</v>
       </c>
       <c r="G16" t="n">
-        <v>2393</v>
+        <v>248</v>
       </c>
       <c r="H16" t="n">
-        <v>14.12</v>
+        <v>1.42</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,47 +1883,47 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>47400</v>
+        <v>13010</v>
       </c>
       <c r="K16" t="n">
-        <v>46350</v>
+        <v>12330</v>
       </c>
       <c r="L16" t="n">
-        <v>47850</v>
+        <v>13560</v>
       </c>
       <c r="M16" t="n">
-        <v>45450</v>
+        <v>12220</v>
       </c>
       <c r="N16" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>45173659075</v>
+        <v>49995282200</v>
       </c>
       <c r="P16" t="n">
-        <v>69200</v>
+        <v>22250</v>
       </c>
       <c r="Q16" t="n">
-        <v>24150</v>
+        <v>6000</v>
       </c>
       <c r="R16" t="n">
-        <v>-61000</v>
+        <v>-152000</v>
       </c>
       <c r="S16" t="n">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성 90% 이상이라는 분석과 함께 초대형 블록버스터 신약 기대감 언급. 공매도 세력에 대한 경계와 함께 시총 100조원 돌파 전망.</t>
+          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['FDA 승인', '공매도', '블록버스터']</t>
+          <t>['유증', '신주상장', '자사주매집']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,187 +1931,187 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12690</v>
+        <v>1725000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.46%</t>
+          <t>'-2.71%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.88</v>
+        <v>-0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>93</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>68</v>
+        <v>445</v>
       </c>
       <c r="G17" t="n">
-        <v>248</v>
+        <v>1872</v>
       </c>
       <c r="H17" t="n">
-        <v>1.42</v>
+        <v>49.71</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13010</v>
+        <v>1773000</v>
       </c>
       <c r="K17" t="n">
-        <v>12330</v>
+        <v>1728000</v>
       </c>
       <c r="L17" t="n">
-        <v>13560</v>
+        <v>1779000</v>
       </c>
       <c r="M17" t="n">
-        <v>12220</v>
+        <v>1725000</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>49.76</v>
       </c>
       <c r="O17" t="n">
-        <v>49487845880</v>
+        <v>3866252951000</v>
       </c>
       <c r="P17" t="n">
-        <v>22250</v>
+        <v>2987000</v>
       </c>
       <c r="Q17" t="n">
-        <v>6000</v>
+        <v>403000</v>
       </c>
       <c r="R17" t="n">
-        <v>-152000</v>
+        <v>-471000</v>
       </c>
       <c r="S17" t="n">
-        <v>16000</v>
+        <v>-89000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
+          <t>외인 및 기관의 지속적인 매도세와 추세선 이탈로 하락 전망이 우세하며, 정치적 이슈와 맞물려 부정적인 심리가 확산되고 있음.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['유증', '신주상장', '자사주매집']</t>
+          <t>['외인 매도', '추세선', '기관']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1728000</v>
+        <v>46100</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.54%</t>
+          <t>'-2.74%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>800</v>
+        <v>377</v>
       </c>
       <c r="F18" t="n">
-        <v>442</v>
+        <v>205</v>
       </c>
       <c r="G18" t="n">
-        <v>1899</v>
+        <v>2467</v>
       </c>
       <c r="H18" t="n">
-        <v>49.71</v>
+        <v>14.12</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1773000</v>
+        <v>47400</v>
       </c>
       <c r="K18" t="n">
-        <v>1728000</v>
+        <v>46350</v>
       </c>
       <c r="L18" t="n">
-        <v>1779000</v>
+        <v>47850</v>
       </c>
       <c r="M18" t="n">
-        <v>1725000</v>
+        <v>45450</v>
       </c>
       <c r="N18" t="n">
-        <v>49.76</v>
+        <v>14.1</v>
       </c>
       <c r="O18" t="n">
-        <v>3740967654500</v>
+        <v>45985891500</v>
       </c>
       <c r="P18" t="n">
-        <v>2987000</v>
+        <v>69200</v>
       </c>
       <c r="Q18" t="n">
-        <v>403000</v>
+        <v>24150</v>
       </c>
       <c r="R18" t="n">
-        <v>-471000</v>
+        <v>-61000</v>
       </c>
       <c r="S18" t="n">
-        <v>-89000</v>
+        <v>2000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>나스닥 하락, 외인 매도세, 공매도 이슈 등으로 추세선이 깨졌다는 분석이 지배적. 정치적 리스크가 주가에 부정적 영향을 미친다는 의견.</t>
+          <t>FDA 승인 가능성 90% 이상이라는 기대감과 함께, 로슈를 뛰어넘는 초대형 블록버스터 신약이 될 것이라는 전망이 제기되며 긍정적인 분위기가 형성되고 있음.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['추세선', '외인매도', '공매도']</t>
+          <t>['FDA 승인', '간암 신약', '매출']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13040</v>
+        <v>13000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.61%</t>
+          <t>'-2.91%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G19" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H19" t="n">
         <v>3.18</v>
@@ -2168,13 +2168,13 @@
         <v>13830</v>
       </c>
       <c r="M19" t="n">
-        <v>13010</v>
+        <v>12960</v>
       </c>
       <c r="N19" t="n">
         <v>3.12</v>
       </c>
       <c r="O19" t="n">
-        <v>27654158875</v>
+        <v>28585892105</v>
       </c>
       <c r="P19" t="n">
         <v>20300</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17860</v>
+        <v>17870</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.62%</t>
+          <t>'-3.56%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1.11</v>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F20" t="n">
         <v>137</v>
       </c>
       <c r="G20" t="n">
-        <v>1165</v>
+        <v>1181</v>
       </c>
       <c r="H20" t="n">
         <v>4.92</v>
@@ -2260,13 +2260,13 @@
         <v>19870</v>
       </c>
       <c r="M20" t="n">
-        <v>17850</v>
+        <v>17840</v>
       </c>
       <c r="N20" t="n">
         <v>3.81</v>
       </c>
       <c r="O20" t="n">
-        <v>287875434790</v>
+        <v>290493124245</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30000</v>
+        <v>29900</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.51%</t>
+          <t>'-5.83%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F21" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G21" t="n">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="H21" t="n">
         <v>10.78</v>
@@ -2352,13 +2352,13 @@
         <v>32850</v>
       </c>
       <c r="M21" t="n">
-        <v>30000</v>
+        <v>29900</v>
       </c>
       <c r="N21" t="n">
         <v>10.77</v>
       </c>
       <c r="O21" t="n">
-        <v>104546219250</v>
+        <v>109494596150</v>
       </c>
       <c r="P21" t="n">
         <v>75900</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>가온전선 대비 큰 폭의 하락세를 보이며 52주 고점 대비 큰 괴리를 나타내는 상황. 개인 투자자들의 매수세와 외인/기관의 매도세가 혼재.</t>
+          <t>가온전선과의 주가 비교를 통해 대한전선의 부진을 지적하며, 개인 투자자들의 매수와 외인 매도세가 겹치며 급락에 대한 우려가 커지고 있음.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['하락세', '개인매수', '외인매도']</t>
+          <t>['주가 비교', '개인 매수', '외인 매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12600</v>
+        <v>12590</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.16%</t>
+          <t>'-8.24%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.43</v>
       </c>
       <c r="E22" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F22" t="n">
         <v>69</v>
       </c>
       <c r="G22" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H22" t="n">
         <v>2.04</v>
@@ -2450,7 +2450,7 @@
         <v>2.47</v>
       </c>
       <c r="O22" t="n">
-        <v>60460010525</v>
+        <v>60765138120</v>
       </c>
       <c r="P22" t="n">
         <v>39600</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>우주 항공 테마 부각 후 급락. 누리호 발사 성공 및 재료 소멸에 대한 언급이 있으며, 공매도 관련 논쟁도 있음.</t>
+          <t>우주항공 테마의 변동성이 큰 가운데, 위성 발사 성공 소식에도 불구하고 재료 소멸 및 매도세로 인한 급락이 이어지며 투자자들의 불만이 고조되고 있음.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['우주항공', '재료소멸', '공매도']</t>
+          <t>['우주항공', '테마', '재료 소멸']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20261007_15.xlsx
+++ b/data/trending_integrated_20261007_15.xlsx
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26447328504</v>
+        <v>26471339104</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>국전</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2755</v>
+        <v>7810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.03%</t>
+          <t>'+15.70%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>93</v>
+        <v>174</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="G3" t="n">
-        <v>122</v>
+        <v>552</v>
       </c>
       <c r="H3" t="n">
-        <v>1.36</v>
+        <v>5.12</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2395</v>
+        <v>6750</v>
       </c>
       <c r="K3" t="n">
-        <v>2410</v>
+        <v>6710</v>
       </c>
       <c r="L3" t="n">
-        <v>3020</v>
+        <v>8450</v>
       </c>
       <c r="M3" t="n">
-        <v>2405</v>
+        <v>6690</v>
       </c>
       <c r="N3" t="n">
-        <v>1.31</v>
+        <v>5.14</v>
       </c>
       <c r="O3" t="n">
-        <v>41288100015</v>
+        <v>143057512355</v>
       </c>
       <c r="P3" t="n">
-        <v>6000</v>
+        <v>23500</v>
       </c>
       <c r="Q3" t="n">
-        <v>1700</v>
+        <v>2890</v>
       </c>
       <c r="R3" t="n">
-        <v>-120000</v>
+        <v>-631000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>흑사병 테마 관련주로 언급되며 거래량은 터졌으나 큰 상승은 못함. 반도체/이차전지 소재 업체로 변신 시도 언급.</t>
+          <t>정부의 용적률 상향 및 그린벨트 해제 발표와 함께 성수동 삼표타워 건설 시작. 만원 돌파 기대감 및 거래량 증가.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['흑사병', '테마주']</t>
+          <t>['용적률', '그린벨트', '거래량']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>307750</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>국전</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7755</v>
+        <v>2750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.89%</t>
+          <t>'+14.82%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>171</v>
+        <v>99</v>
       </c>
       <c r="F4" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>548</v>
+        <v>126</v>
       </c>
       <c r="H4" t="n">
-        <v>5.12</v>
+        <v>1.36</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6750</v>
+        <v>2395</v>
       </c>
       <c r="K4" t="n">
-        <v>6710</v>
+        <v>2410</v>
       </c>
       <c r="L4" t="n">
-        <v>8450</v>
+        <v>3020</v>
       </c>
       <c r="M4" t="n">
-        <v>6690</v>
+        <v>2405</v>
       </c>
       <c r="N4" t="n">
-        <v>5.14</v>
+        <v>1.31</v>
       </c>
       <c r="O4" t="n">
-        <v>141547431725</v>
+        <v>41518463695</v>
       </c>
       <c r="P4" t="n">
-        <v>23500</v>
+        <v>6000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2890</v>
+        <v>1700</v>
       </c>
       <c r="R4" t="n">
-        <v>-631000</v>
+        <v>-120000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부의 용적률 상향 및 그린벨트 해제 발표와 함께 성수동 삼표타워 건설 시작. 만원 돌파 기대감 및 거래량 증가.</t>
+          <t>흑사병 테마 관련주로 언급되며 거래량은 터졌으나 큰 상승은 못함. 반도체/이차전지 소재 업체로 변신 시도 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['용적률', '그린벨트', '거래량']</t>
+          <t>['흑사병', '테마주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,12 +827,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>307750</t>
         </is>
       </c>
     </row>
@@ -854,13 +854,13 @@
         <v>0.17</v>
       </c>
       <c r="E5" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G5" t="n">
-        <v>539</v>
+        <v>563</v>
       </c>
       <c r="H5" t="n">
         <v>5.01</v>
@@ -886,7 +886,7 @@
         <v>4.84</v>
       </c>
       <c r="O5" t="n">
-        <v>31997231395</v>
+        <v>32678797020</v>
       </c>
       <c r="P5" t="n">
         <v>15900</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>러시아 흑사병 사망자 발생 소식에 신풍제약이 테마주로 부각되며 급등, 과거 코로나 시절의 경험을 바탕으로 기대감이 형성되고 있음.</t>
+          <t>흑사병, 페스트 관련 테마주로 부각되며 사망자 발생 및 확산 우려 속 치료제 생산 업체로서 기대감 형성. 프로그램 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['흑사병', '테마주', '급등']</t>
+          <t>['흑사병', '테마주', '치료제']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25600</v>
+        <v>16680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.55%</t>
+          <t>'+12.17%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.98</v>
       </c>
       <c r="E6" t="n">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="G6" t="n">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="H6" t="n">
-        <v>2.82</v>
+        <v>2.37</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>22950</v>
+        <v>14870</v>
       </c>
       <c r="K6" t="n">
-        <v>26200</v>
+        <v>15480</v>
       </c>
       <c r="L6" t="n">
-        <v>27600</v>
+        <v>17590</v>
       </c>
       <c r="M6" t="n">
-        <v>25550</v>
+        <v>14600</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>1.39</v>
       </c>
       <c r="O6" t="n">
-        <v>104902500825</v>
+        <v>295169446390</v>
       </c>
       <c r="P6" t="n">
-        <v>30100</v>
+        <v>17590</v>
       </c>
       <c r="Q6" t="n">
-        <v>11140</v>
+        <v>6320</v>
       </c>
       <c r="R6" t="n">
-        <v>160000</v>
+        <v>-95000</v>
       </c>
       <c r="S6" t="n">
-        <v>-227000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>유리 기술력 기반 성장 기대감. 브로드컴, 씨게이트 등 대기업과의 협력 가능성.</t>
+          <t>개인정보 유출 및 보안 이슈 부각에 따른 보안주 강세. NH농협, KDB생명 등에 대한 양자보안 공급 논의 및 10곳 이상 공급 예상.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유리', '기술력', '협력']</t>
+          <t>['양자보안', '개인정보유출', '공급']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13750</v>
+        <v>25700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+11.52%</t>
+          <t>'+11.98%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.31</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="F7" t="n">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="H7" t="n">
-        <v>0.79</v>
+        <v>2.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>12330</v>
+        <v>22950</v>
       </c>
       <c r="K7" t="n">
-        <v>12580</v>
+        <v>26200</v>
       </c>
       <c r="L7" t="n">
-        <v>14260</v>
+        <v>27600</v>
       </c>
       <c r="M7" t="n">
-        <v>12300</v>
+        <v>25550</v>
       </c>
       <c r="N7" t="n">
-        <v>0.48</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
-        <v>228577797640</v>
+        <v>105883920175</v>
       </c>
       <c r="P7" t="n">
-        <v>20850</v>
+        <v>30100</v>
       </c>
       <c r="Q7" t="n">
-        <v>4020</v>
+        <v>11140</v>
       </c>
       <c r="R7" t="n">
-        <v>-68000</v>
+        <v>160000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-227000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>한화파워향 가스터빈 블레이드 첫 납품 뉴스가 나왔으나, 주포의 이탈 및 일부 투자자들의 부정적 전망과 함께 변동성이 큰 하루를 보임.</t>
+          <t>유리 기술력 기반 성장 기대감. 브로드컴, 씨게이트 등 대기업과의 협력 가능성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['가스터빈', '납품', '뉴스']</t>
+          <t>['유리', '기술력', '협력']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,43 +1103,43 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16570</v>
+        <v>13650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+11.43%</t>
+          <t>'+10.71%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.98</v>
+        <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>204</v>
+        <v>131</v>
       </c>
       <c r="F8" t="n">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>345</v>
+        <v>277</v>
       </c>
       <c r="H8" t="n">
-        <v>2.37</v>
+        <v>0.79</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14870</v>
+        <v>12330</v>
       </c>
       <c r="K8" t="n">
-        <v>15480</v>
+        <v>12580</v>
       </c>
       <c r="L8" t="n">
-        <v>17590</v>
+        <v>14260</v>
       </c>
       <c r="M8" t="n">
-        <v>14600</v>
+        <v>12300</v>
       </c>
       <c r="N8" t="n">
-        <v>1.39</v>
+        <v>0.48</v>
       </c>
       <c r="O8" t="n">
-        <v>293227829885</v>
+        <v>231193691595</v>
       </c>
       <c r="P8" t="n">
-        <v>17590</v>
+        <v>20850</v>
       </c>
       <c r="Q8" t="n">
-        <v>6320</v>
+        <v>4020</v>
       </c>
       <c r="R8" t="n">
-        <v>-95000</v>
+        <v>-68000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>국내외 해킹·보안 이슈 부각 속 라온시큐어 상승. 농협·KDB생명 해킹 방어 및 양자보안 공급 논의.</t>
+          <t>한화파워향 가스터빈 블레이드 첫 납품 뉴스가 나왔으나, 주포의 이탈 및 일부 투자자들의 부정적 전망과 함께 변동성이 큰 하루를 보임.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['양자보안', '해킹', '보안주']</t>
+          <t>['가스터빈', '납품', '뉴스']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2600</v>
+        <v>2595</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+9.01%</t>
+          <t>'+8.81%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.29</v>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
         <v>95</v>
@@ -1254,7 +1254,7 @@
         <v>1.11</v>
       </c>
       <c r="O9" t="n">
-        <v>15490884448</v>
+        <v>15604956838</v>
       </c>
       <c r="P9" t="n">
         <v>4760</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5200</v>
+        <v>5210</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.79%</t>
+          <t>'+3.99%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>3.32</v>
       </c>
       <c r="E10" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F10" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G10" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="H10" t="n">
         <v>4.72</v>
@@ -1346,7 +1346,7 @@
         <v>1.4</v>
       </c>
       <c r="O10" t="n">
-        <v>243439565595</v>
+        <v>245082518530</v>
       </c>
       <c r="P10" t="n">
         <v>8100</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시 호조와 더불어 엠바고 해제 시 2200억 규모의 선주문 발주서 기준 물량에 대한 기대감으로 상승 가능성이 언급되고 있으나, 일부 투자자는 물려있는 상황.</t>
+          <t>미국 증시 호조 및 시에나, 루멘텀 등 관련주 상승세에 대한 기대감. 엠바고 해제 및 2200억 규모 선주문 발주서 기준 확인.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['선주문', '발주서', '미국 증시']</t>
+          <t>['미국증시', '선주문', '엠바고']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>243500</v>
+        <v>241500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.04%</t>
+          <t>'+0.21%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>227</v>
       </c>
       <c r="F11" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G11" t="n">
-        <v>1249</v>
+        <v>1273</v>
       </c>
       <c r="H11" t="n">
         <v>4.12</v>
@@ -1438,7 +1438,7 @@
         <v>4.08</v>
       </c>
       <c r="O11" t="n">
-        <v>105155064500</v>
+        <v>106372965250</v>
       </c>
       <c r="P11" t="n">
         <v>1233000</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6980</v>
+        <v>6990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.14%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>59</v>
       </c>
       <c r="G12" t="n">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="H12" t="n">
         <v>1.1</v>
@@ -1530,7 +1530,7 @@
         <v>1.87</v>
       </c>
       <c r="O12" t="n">
-        <v>72889559255</v>
+        <v>73708314765</v>
       </c>
       <c r="P12" t="n">
         <v>11370</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>269000</v>
+        <v>269500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.10%</t>
+          <t>'-0.92%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="G13" t="n">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H13" t="n">
         <v>46.37</v>
@@ -1622,7 +1622,7 @@
         <v>46.41</v>
       </c>
       <c r="O13" t="n">
-        <v>3885476579500</v>
+        <v>3987122550000</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>AMD CEO의 HBM 대량 주문 및 파운드리 계약 소식에도 불구하고, 투자자들은 실적 전망 및 외인/국장 매도세에 대한 우려를 표하며 부정적인 전망을 보임.</t>
+          <t>AMD CEO 방한 및 HBM 대량 주문, 파운드리 계약 소식과 함께 삼성전자 실적 110조 이상 전망. 하지만 외인 및 국장 매도세 지속 및 정치적 언급 다수.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80400</v>
+        <v>80500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.35%</t>
+          <t>'-1.23%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F14" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G14" t="n">
-        <v>907</v>
+        <v>917</v>
       </c>
       <c r="H14" t="n">
         <v>22.59</v>
@@ -1714,7 +1714,7 @@
         <v>22.56</v>
       </c>
       <c r="O14" t="n">
-        <v>168322636000</v>
+        <v>172354169500</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17370</v>
+        <v>17340</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.14%</t>
+          <t>'-2.31%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G15" t="n">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="H15" t="n">
         <v>9.5</v>
@@ -1800,13 +1800,13 @@
         <v>18030</v>
       </c>
       <c r="M15" t="n">
-        <v>17370</v>
+        <v>17330</v>
       </c>
       <c r="N15" t="n">
         <v>9.390000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>58389197265</v>
+        <v>60446889610</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1851,368 +1851,368 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12700</v>
+        <v>1728000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.38%</t>
+          <t>'-2.54%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.88</v>
+        <v>-0.05</v>
       </c>
       <c r="E16" t="n">
-        <v>92</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>67</v>
+        <v>439</v>
       </c>
       <c r="G16" t="n">
-        <v>248</v>
+        <v>1851</v>
       </c>
       <c r="H16" t="n">
-        <v>1.42</v>
+        <v>49.71</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13010</v>
+        <v>1773000</v>
       </c>
       <c r="K16" t="n">
-        <v>12330</v>
+        <v>1728000</v>
       </c>
       <c r="L16" t="n">
-        <v>13560</v>
+        <v>1779000</v>
       </c>
       <c r="M16" t="n">
-        <v>12220</v>
+        <v>1724000</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>49.76</v>
       </c>
       <c r="O16" t="n">
-        <v>49995282200</v>
+        <v>3975558883000</v>
       </c>
       <c r="P16" t="n">
-        <v>22250</v>
+        <v>2987000</v>
       </c>
       <c r="Q16" t="n">
-        <v>6000</v>
+        <v>403000</v>
       </c>
       <c r="R16" t="n">
-        <v>-152000</v>
+        <v>-471000</v>
       </c>
       <c r="S16" t="n">
-        <v>16000</v>
+        <v>-89000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
+          <t>외인 및 기관의 지속적인 매도세와 추세선 이탈로 하락 전망이 우세하며, 정치적 이슈와 맞물려 부정적인 심리가 확산되고 있음.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['유증', '신주상장', '자사주매집']</t>
+          <t>['외인 매도', '추세선', '기관']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1725000</v>
+        <v>12640</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.71%</t>
+          <t>'-2.84%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.05</v>
+        <v>1.88</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>92</v>
       </c>
       <c r="F17" t="n">
-        <v>445</v>
+        <v>67</v>
       </c>
       <c r="G17" t="n">
-        <v>1872</v>
+        <v>263</v>
       </c>
       <c r="H17" t="n">
-        <v>49.71</v>
+        <v>1.42</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1773000</v>
+        <v>13010</v>
       </c>
       <c r="K17" t="n">
-        <v>1728000</v>
+        <v>12330</v>
       </c>
       <c r="L17" t="n">
-        <v>1779000</v>
+        <v>13560</v>
       </c>
       <c r="M17" t="n">
-        <v>1725000</v>
+        <v>12220</v>
       </c>
       <c r="N17" t="n">
-        <v>49.76</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3866252951000</v>
+        <v>50387926480</v>
       </c>
       <c r="P17" t="n">
-        <v>2987000</v>
+        <v>22250</v>
       </c>
       <c r="Q17" t="n">
-        <v>403000</v>
+        <v>6000</v>
       </c>
       <c r="R17" t="n">
-        <v>-471000</v>
+        <v>-152000</v>
       </c>
       <c r="S17" t="n">
-        <v>-89000</v>
+        <v>16000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>외인 및 기관의 지속적인 매도세와 추세선 이탈로 하락 전망이 우세하며, 정치적 이슈와 맞물려 부정적인 심리가 확산되고 있음.</t>
+          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['외인 매도', '추세선', '기관']</t>
+          <t>['유증', '신주상장', '자사주매집']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46100</v>
+        <v>13000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.74%</t>
+          <t>'-2.91%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>377</v>
+        <v>56</v>
       </c>
       <c r="F18" t="n">
-        <v>205</v>
+        <v>23</v>
       </c>
       <c r="G18" t="n">
-        <v>2467</v>
+        <v>89</v>
       </c>
       <c r="H18" t="n">
-        <v>14.12</v>
+        <v>3.18</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>47400</v>
+        <v>13390</v>
       </c>
       <c r="K18" t="n">
-        <v>46350</v>
+        <v>13770</v>
       </c>
       <c r="L18" t="n">
-        <v>47850</v>
+        <v>13830</v>
       </c>
       <c r="M18" t="n">
-        <v>45450</v>
+        <v>12950</v>
       </c>
       <c r="N18" t="n">
-        <v>14.1</v>
+        <v>3.12</v>
       </c>
       <c r="O18" t="n">
-        <v>45985891500</v>
+        <v>28980943380</v>
       </c>
       <c r="P18" t="n">
-        <v>69200</v>
+        <v>20300</v>
       </c>
       <c r="Q18" t="n">
-        <v>24150</v>
+        <v>3020</v>
       </c>
       <c r="R18" t="n">
-        <v>-61000</v>
+        <v>-313000</v>
       </c>
       <c r="S18" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성 90% 이상이라는 기대감과 함께, 로슈를 뛰어넘는 초대형 블록버스터 신약이 될 것이라는 전망이 제기되며 긍정적인 분위기가 형성되고 있음.</t>
+          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암 신약', '매출']</t>
+          <t>['전선주', '박스권', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13000</v>
+        <v>46000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.91%</t>
+          <t>'-2.95%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>55</v>
+        <v>382</v>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>207</v>
       </c>
       <c r="G19" t="n">
-        <v>84</v>
+        <v>2484</v>
       </c>
       <c r="H19" t="n">
-        <v>3.18</v>
+        <v>14.12</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>13390</v>
+        <v>47400</v>
       </c>
       <c r="K19" t="n">
-        <v>13770</v>
+        <v>46350</v>
       </c>
       <c r="L19" t="n">
-        <v>13830</v>
+        <v>47850</v>
       </c>
       <c r="M19" t="n">
-        <v>12960</v>
+        <v>45450</v>
       </c>
       <c r="N19" t="n">
-        <v>3.12</v>
+        <v>14.1</v>
       </c>
       <c r="O19" t="n">
-        <v>28585892105</v>
+        <v>46410327950</v>
       </c>
       <c r="P19" t="n">
-        <v>20300</v>
+        <v>69200</v>
       </c>
       <c r="Q19" t="n">
-        <v>3020</v>
+        <v>24150</v>
       </c>
       <c r="R19" t="n">
-        <v>-313000</v>
+        <v>-61000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
+          <t>FDA 승인 가능성 90% 이상이라는 기대감과 함께, 로슈를 뛰어넘는 초대형 블록버스터 신약이 될 것이라는 전망이 제기되며 긍정적인 분위기가 형성되고 있음.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['전선주', '박스권', '공매도']</t>
+          <t>['FDA 승인', '간암 신약', '매출']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17870</v>
+        <v>17930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.56%</t>
+          <t>'-3.24%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1.11</v>
       </c>
       <c r="E20" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F20" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G20" t="n">
-        <v>1181</v>
+        <v>1226</v>
       </c>
       <c r="H20" t="n">
         <v>4.92</v>
@@ -2266,7 +2266,7 @@
         <v>3.81</v>
       </c>
       <c r="O20" t="n">
-        <v>290493124245</v>
+        <v>292194908030</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 상승 및 젠슨황의 광통신 지지 언급 등 긍정적 뉴스에도 불구하고, 외인 대량 매도와 프로그램 매매 상황에 대한 우려.</t>
+          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 관련 언급. 5만원 목표가 제시 및 외인 대량 매도세 포착.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['광통신', '외인매도', '젠슨황']</t>
+          <t>['광통신', '젠슨황', '외인매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29900</v>
+        <v>29850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.83%</t>
+          <t>'-5.98%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F21" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G21" t="n">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="H21" t="n">
         <v>10.78</v>
@@ -2352,13 +2352,13 @@
         <v>32850</v>
       </c>
       <c r="M21" t="n">
-        <v>29900</v>
+        <v>29800</v>
       </c>
       <c r="N21" t="n">
         <v>10.77</v>
       </c>
       <c r="O21" t="n">
-        <v>109494596150</v>
+        <v>112400301825</v>
       </c>
       <c r="P21" t="n">
         <v>75900</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>가온전선과의 주가 비교를 통해 대한전선의 부진을 지적하며, 개인 투자자들의 매수와 외인 매도세가 겹치며 급락에 대한 우려가 커지고 있음.</t>
+          <t>가온전선과의 비교에서 실력 및 기술력 차이 언급. 52주 고점 대비 큰 폭 하락 및 개인 매수세 지적. 외인 매도 물량 확인.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주가 비교', '개인 매수', '외인 매도']</t>
+          <t>['고점대비', '실력차이', '외인매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12590</v>
+        <v>12460</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.24%</t>
+          <t>'-9.18%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.43</v>
       </c>
       <c r="E22" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F22" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G22" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H22" t="n">
         <v>2.04</v>
@@ -2444,13 +2444,13 @@
         <v>14650</v>
       </c>
       <c r="M22" t="n">
-        <v>12500</v>
+        <v>12450</v>
       </c>
       <c r="N22" t="n">
         <v>2.47</v>
       </c>
       <c r="O22" t="n">
-        <v>60765138120</v>
+        <v>61106296705</v>
       </c>
       <c r="P22" t="n">
         <v>39600</v>

--- a/data/trending_integrated_20261007_15.xlsx
+++ b/data/trending_integrated_20261007_15.xlsx
@@ -578,7 +578,7 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F2" t="n">
         <v>52</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26471339104</v>
+        <v>26477775894</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7810</v>
+        <v>7820</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.70%</t>
+          <t>'+15.85%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="F3" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>552</v>
+        <v>577</v>
       </c>
       <c r="H3" t="n">
         <v>5.12</v>
@@ -702,7 +702,7 @@
         <v>5.14</v>
       </c>
       <c r="O3" t="n">
-        <v>143057512355</v>
+        <v>143870503015</v>
       </c>
       <c r="P3" t="n">
         <v>23500</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2750</v>
+        <v>2770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.82%</t>
+          <t>'+15.66%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
         <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H4" t="n">
         <v>1.36</v>
@@ -794,7 +794,7 @@
         <v>1.31</v>
       </c>
       <c r="O4" t="n">
-        <v>41518463695</v>
+        <v>41630078075</v>
       </c>
       <c r="P4" t="n">
         <v>6000</v>
@@ -854,13 +854,13 @@
         <v>0.17</v>
       </c>
       <c r="E5" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F5" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G5" t="n">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H5" t="n">
         <v>5.01</v>
@@ -886,7 +886,7 @@
         <v>4.84</v>
       </c>
       <c r="O5" t="n">
-        <v>32678797020</v>
+        <v>33031909740</v>
       </c>
       <c r="P5" t="n">
         <v>15900</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16680</v>
+        <v>25800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.17%</t>
+          <t>'+12.42%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.98</v>
+        <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>201</v>
+        <v>102</v>
       </c>
       <c r="F6" t="n">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>348</v>
+        <v>310</v>
       </c>
       <c r="H6" t="n">
-        <v>2.37</v>
+        <v>2.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14870</v>
+        <v>22950</v>
       </c>
       <c r="K6" t="n">
-        <v>15480</v>
+        <v>26200</v>
       </c>
       <c r="L6" t="n">
-        <v>17590</v>
+        <v>27600</v>
       </c>
       <c r="M6" t="n">
-        <v>14600</v>
+        <v>25550</v>
       </c>
       <c r="N6" t="n">
-        <v>1.39</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>295169446390</v>
+        <v>106259052175</v>
       </c>
       <c r="P6" t="n">
-        <v>17590</v>
+        <v>30100</v>
       </c>
       <c r="Q6" t="n">
-        <v>6320</v>
+        <v>11140</v>
       </c>
       <c r="R6" t="n">
-        <v>-95000</v>
+        <v>160000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-227000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>개인정보 유출 및 보안 이슈 부각에 따른 보안주 강세. NH농협, KDB생명 등에 대한 양자보안 공급 논의 및 10곳 이상 공급 예상.</t>
+          <t>유리 기술력 기반 성장 기대감. 브로드컴, 씨게이트 등 대기업과의 협력 가능성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['양자보안', '개인정보유출', '공급']</t>
+          <t>['유리', '기술력', '협력']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25700</v>
+        <v>16710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+11.98%</t>
+          <t>'+12.37%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>0.98</v>
       </c>
       <c r="E7" t="n">
-        <v>99</v>
+        <v>198</v>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="G7" t="n">
-        <v>307</v>
+        <v>356</v>
       </c>
       <c r="H7" t="n">
-        <v>2.82</v>
+        <v>2.37</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>22950</v>
+        <v>14870</v>
       </c>
       <c r="K7" t="n">
-        <v>26200</v>
+        <v>15480</v>
       </c>
       <c r="L7" t="n">
-        <v>27600</v>
+        <v>17590</v>
       </c>
       <c r="M7" t="n">
-        <v>25550</v>
+        <v>14600</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>1.39</v>
       </c>
       <c r="O7" t="n">
-        <v>105883920175</v>
+        <v>295688609380</v>
       </c>
       <c r="P7" t="n">
-        <v>30100</v>
+        <v>17590</v>
       </c>
       <c r="Q7" t="n">
-        <v>11140</v>
+        <v>6320</v>
       </c>
       <c r="R7" t="n">
-        <v>160000</v>
+        <v>-95000</v>
       </c>
       <c r="S7" t="n">
-        <v>-227000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유리 기술력 기반 성장 기대감. 브로드컴, 씨게이트 등 대기업과의 협력 가능성.</t>
+          <t>개인정보 유출 이슈와 함께 미국 보안주 상승, 양자보안 공급 논의 등 긍정적인 뉴스 및 기술적 분석 언급. 보안 이슈 부각 및 주포 움직임에 대한 기대감 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유리', '기술력', '협력']</t>
+          <t>['라온시큐어', '양자보안', '해킹']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13650</v>
+        <v>13720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+10.71%</t>
+          <t>'+11.27%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F8" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G8" t="n">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="H8" t="n">
         <v>0.79</v>
@@ -1162,7 +1162,7 @@
         <v>0.48</v>
       </c>
       <c r="O8" t="n">
-        <v>231193691595</v>
+        <v>231815029235</v>
       </c>
       <c r="P8" t="n">
         <v>20850</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>한화파워향 가스터빈 블레이드 첫 납품 뉴스가 나왔으나, 주포의 이탈 및 일부 투자자들의 부정적 전망과 함께 변동성이 큰 하루를 보임.</t>
+          <t>한화파워향 가스터빈 블레이드 첫 납품 공시가 있었으나, 주가 부양보다는 개미 물량 확보에 집중하는 듯한 움직임을 보이며 긍정적/부정적 의견이 혼재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['가스터빈', '납품', '뉴스']</t>
+          <t>['삼미금속', '가스터빈', '납품']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2595</v>
+        <v>2590</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.81%</t>
+          <t>'+8.60%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H9" t="n">
         <v>0.82</v>
@@ -1254,7 +1254,7 @@
         <v>1.11</v>
       </c>
       <c r="O9" t="n">
-        <v>15604956838</v>
+        <v>15648564668</v>
       </c>
       <c r="P9" t="n">
         <v>4760</v>
@@ -1317,10 +1317,10 @@
         <v>233</v>
       </c>
       <c r="F10" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G10" t="n">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="H10" t="n">
         <v>4.72</v>
@@ -1346,7 +1346,7 @@
         <v>1.4</v>
       </c>
       <c r="O10" t="n">
-        <v>245082518530</v>
+        <v>245726776710</v>
       </c>
       <c r="P10" t="n">
         <v>8100</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시 호조 및 시에나, 루멘텀 등 관련주 상승세에 대한 기대감. 엠바고 해제 및 2200억 규모 선주문 발주서 기준 확인.</t>
+          <t>미국 증시 호조와 더불어 엠바고 해제 시 2200억 규모의 선주문 발주서 기준 물량에 대한 기대감으로 상승 가능성이 언급되고 있으나, 일부 투자자는 물려있는 상황.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['미국증시', '선주문', '엠바고']</t>
+          <t>['선주문', '발주서', '미국 증시']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>241500</v>
+        <v>6990</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.21%</t>
+          <t>'+0.14%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.04</v>
+        <v>-0.77</v>
       </c>
       <c r="E11" t="n">
-        <v>227</v>
+        <v>95</v>
       </c>
       <c r="F11" t="n">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>1273</v>
+        <v>243</v>
       </c>
       <c r="H11" t="n">
-        <v>4.12</v>
+        <v>1.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>241000</v>
+        <v>6980</v>
       </c>
       <c r="K11" t="n">
-        <v>253000</v>
+        <v>7000</v>
       </c>
       <c r="L11" t="n">
-        <v>257000</v>
+        <v>7240</v>
       </c>
       <c r="M11" t="n">
-        <v>233500</v>
+        <v>6580</v>
       </c>
       <c r="N11" t="n">
-        <v>4.08</v>
+        <v>1.87</v>
       </c>
       <c r="O11" t="n">
-        <v>106372965250</v>
+        <v>74222883615</v>
       </c>
       <c r="P11" t="n">
-        <v>1233000</v>
+        <v>11370</v>
       </c>
       <c r="Q11" t="n">
-        <v>120000</v>
+        <v>3300</v>
       </c>
       <c r="R11" t="n">
-        <v>-78000</v>
+        <v>20000</v>
       </c>
       <c r="S11" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>아일리아 관련 기대감과 함께 경구용 인슐린 10조원대 L/O 예상, 캐나다 및 독일 계약 공시 가능성이 언급됨.</t>
+          <t>보안주로 분류되며 금융권 공략 뉴스 부각. 라온시큐어와의 비교 언급 및 거래량 대비 주가 움직임에 대한 아쉬움 표출.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['아일리아', '경구용 인슐린', '계약 공시']</t>
+          <t>['보안', '금융권']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6990</v>
+        <v>241000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.14%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.77</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>93</v>
+        <v>228</v>
       </c>
       <c r="F12" t="n">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="G12" t="n">
-        <v>238</v>
+        <v>1298</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1</v>
+        <v>4.12</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,91 +1515,91 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>6980</v>
+        <v>241000</v>
       </c>
       <c r="K12" t="n">
-        <v>7000</v>
+        <v>253000</v>
       </c>
       <c r="L12" t="n">
-        <v>7240</v>
+        <v>257000</v>
       </c>
       <c r="M12" t="n">
-        <v>6580</v>
+        <v>233500</v>
       </c>
       <c r="N12" t="n">
-        <v>1.87</v>
+        <v>4.08</v>
       </c>
       <c r="O12" t="n">
-        <v>73708314765</v>
+        <v>107346123250</v>
       </c>
       <c r="P12" t="n">
-        <v>11370</v>
+        <v>1233000</v>
       </c>
       <c r="Q12" t="n">
-        <v>3300</v>
+        <v>120000</v>
       </c>
       <c r="R12" t="n">
-        <v>20000</v>
+        <v>-78000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>보안주로 분류되며 금융권 공략 뉴스 부각. 라온시큐어와의 비교 언급 및 거래량 대비 주가 움직임에 대한 아쉬움 표출.</t>
+          <t>아일리아, 경구용 인슐린 관련 기대감이 높으며, 릴레이 계약 공시 및 외국인 수급에 대한 긍정적인 전망이 제시됨. 거래량 동반 시 상승 기대감 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['보안', '금융권']</t>
+          <t>['삼천당제약', '아일리아', '경구용 인슐린']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>269500</v>
+        <v>80500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.92%</t>
+          <t>'-1.23%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>348</v>
       </c>
       <c r="F13" t="n">
-        <v>495</v>
+        <v>181</v>
       </c>
       <c r="G13" t="n">
-        <v>1298</v>
+        <v>917</v>
       </c>
       <c r="H13" t="n">
-        <v>46.37</v>
+        <v>22.59</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>272000</v>
+        <v>81500</v>
       </c>
       <c r="K13" t="n">
-        <v>269500</v>
+        <v>83500</v>
       </c>
       <c r="L13" t="n">
-        <v>279500</v>
+        <v>84300</v>
       </c>
       <c r="M13" t="n">
-        <v>268500</v>
+        <v>80200</v>
       </c>
       <c r="N13" t="n">
-        <v>46.41</v>
+        <v>22.56</v>
       </c>
       <c r="O13" t="n">
-        <v>3987122550000</v>
+        <v>178558868000</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>90200</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>1548000</v>
+        <v>-231000</v>
       </c>
       <c r="S13" t="n">
-        <v>-319000</v>
+        <v>-52000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>AMD CEO 방한 및 HBM 대량 주문, 파운드리 계약 소식과 함께 삼성전자 실적 110조 이상 전망. 하지만 외인 및 국장 매도세 지속 및 정치적 언급 다수.</t>
+          <t>미국 원전주 급등 및 구글의 전력구매 계약 체결 관련 호재. 공매도 박살 기대감 및 상승 여력.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['HBM', '파운드리', '실적']</t>
+          <t>['원전주', '전력구매계약', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80500</v>
+        <v>268500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.23%</t>
+          <t>'-1.29%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>346</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>181</v>
+        <v>488</v>
       </c>
       <c r="G14" t="n">
-        <v>917</v>
+        <v>1324</v>
       </c>
       <c r="H14" t="n">
-        <v>22.59</v>
+        <v>46.37</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>81500</v>
+        <v>272000</v>
       </c>
       <c r="K14" t="n">
-        <v>83500</v>
+        <v>269500</v>
       </c>
       <c r="L14" t="n">
-        <v>84300</v>
+        <v>279500</v>
       </c>
       <c r="M14" t="n">
-        <v>80200</v>
+        <v>268500</v>
       </c>
       <c r="N14" t="n">
-        <v>22.56</v>
+        <v>46.41</v>
       </c>
       <c r="O14" t="n">
-        <v>172354169500</v>
+        <v>4347472909500</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>90200</v>
       </c>
       <c r="R14" t="n">
-        <v>-231000</v>
+        <v>1548000</v>
       </c>
       <c r="S14" t="n">
-        <v>-52000</v>
+        <v>-319000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 구글의 전력구매 계약 체결 관련 호재. 공매도 박살 기대감 및 상승 여력.</t>
+          <t>AMD CEO의 HBM 대량 주문 및 파운드리 계약 소식에도 불구하고, 정치적 발언과 개인적인 비난이 주를 이루며 객관적인 사실 기반의 분석은 부족함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전주', '전력구매계약', '공매도']</t>
+          <t>['HBM', '파운드리', 'AMD']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1774,13 +1774,13 @@
         <v>0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="H15" t="n">
         <v>9.5</v>
@@ -1806,7 +1806,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>60446889610</v>
+        <v>61184533210</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1728000</v>
+        <v>1723000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.54%</t>
+          <t>'-2.82%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G16" t="n">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="H16" t="n">
         <v>49.71</v>
@@ -1892,13 +1892,13 @@
         <v>1779000</v>
       </c>
       <c r="M16" t="n">
-        <v>1724000</v>
+        <v>1723000</v>
       </c>
       <c r="N16" t="n">
         <v>49.76</v>
       </c>
       <c r="O16" t="n">
-        <v>3975558883000</v>
+        <v>4388098496000</v>
       </c>
       <c r="P16" t="n">
         <v>2987000</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>외인 및 기관의 지속적인 매도세와 추세선 이탈로 하락 전망이 우세하며, 정치적 이슈와 맞물려 부정적인 심리가 확산되고 있음.</t>
+          <t>나스닥 하락, 외인 매도세, 추세선 이탈 등 부정적인 요인과 함께 향후 주가 하락을 예견하는 의견이 많음. 객관적 근거는 일부 있으나 부정적 전망이 우세.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['외인 매도', '추세선', '기관']</t>
+          <t>['SK하이닉스', '외인매도', '추세선']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12640</v>
+        <v>45900</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.84%</t>
+          <t>'-3.16%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.88</v>
+        <v>0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>92</v>
+        <v>385</v>
       </c>
       <c r="F17" t="n">
-        <v>67</v>
+        <v>207</v>
       </c>
       <c r="G17" t="n">
-        <v>263</v>
+        <v>2505</v>
       </c>
       <c r="H17" t="n">
-        <v>1.42</v>
+        <v>14.12</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,47 +1975,47 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13010</v>
+        <v>47400</v>
       </c>
       <c r="K17" t="n">
-        <v>12330</v>
+        <v>46350</v>
       </c>
       <c r="L17" t="n">
-        <v>13560</v>
+        <v>47850</v>
       </c>
       <c r="M17" t="n">
-        <v>12220</v>
+        <v>45450</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="O17" t="n">
-        <v>50387926480</v>
+        <v>47317266050</v>
       </c>
       <c r="P17" t="n">
-        <v>22250</v>
+        <v>69200</v>
       </c>
       <c r="Q17" t="n">
-        <v>6000</v>
+        <v>24150</v>
       </c>
       <c r="R17" t="n">
-        <v>-152000</v>
+        <v>-61000</v>
       </c>
       <c r="S17" t="n">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
+          <t>FDA 승인 가능성 90% 이상, 연 매출 2~3조원 예상 등 구체적인 근거와 함께 신약 개발에 대한 높은 기대감이 반영됨. 공매도 관련 언급도 존재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['유증', '신주상장', '자사주매집']</t>
+          <t>['HLB', 'FDA', '간암 신약']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,227 +2023,227 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13000</v>
+        <v>17940</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.91%</t>
+          <t>'-3.18%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.06</v>
+        <v>1.11</v>
       </c>
       <c r="E18" t="n">
-        <v>56</v>
+        <v>215</v>
       </c>
       <c r="F18" t="n">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G18" t="n">
-        <v>89</v>
+        <v>1246</v>
       </c>
       <c r="H18" t="n">
-        <v>3.18</v>
+        <v>4.92</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13390</v>
+        <v>18530</v>
       </c>
       <c r="K18" t="n">
-        <v>13770</v>
+        <v>18950</v>
       </c>
       <c r="L18" t="n">
-        <v>13830</v>
+        <v>19870</v>
       </c>
       <c r="M18" t="n">
-        <v>12950</v>
+        <v>17840</v>
       </c>
       <c r="N18" t="n">
-        <v>3.12</v>
+        <v>3.81</v>
       </c>
       <c r="O18" t="n">
-        <v>28980943380</v>
+        <v>292916741870</v>
       </c>
       <c r="P18" t="n">
-        <v>20300</v>
+        <v>31500</v>
       </c>
       <c r="Q18" t="n">
-        <v>3020</v>
+        <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>-313000</v>
+        <v>-479000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
+          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 관련 언급. 5만원 목표가 제시 및 외인 대량 매도세 포착.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['전선주', '박스권', '공매도']</t>
+          <t>['광통신', '젠슨황', '외인매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>46000</v>
+        <v>12950</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.95%</t>
+          <t>'-3.29%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>382</v>
+        <v>58</v>
       </c>
       <c r="F19" t="n">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
-        <v>2484</v>
+        <v>94</v>
       </c>
       <c r="H19" t="n">
-        <v>14.12</v>
+        <v>3.18</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>47400</v>
+        <v>13390</v>
       </c>
       <c r="K19" t="n">
-        <v>46350</v>
+        <v>13770</v>
       </c>
       <c r="L19" t="n">
-        <v>47850</v>
+        <v>13830</v>
       </c>
       <c r="M19" t="n">
-        <v>45450</v>
+        <v>12950</v>
       </c>
       <c r="N19" t="n">
-        <v>14.1</v>
+        <v>3.12</v>
       </c>
       <c r="O19" t="n">
-        <v>46410327950</v>
+        <v>29215985880</v>
       </c>
       <c r="P19" t="n">
-        <v>69200</v>
+        <v>20300</v>
       </c>
       <c r="Q19" t="n">
-        <v>24150</v>
+        <v>3020</v>
       </c>
       <c r="R19" t="n">
-        <v>-61000</v>
+        <v>-313000</v>
       </c>
       <c r="S19" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성 90% 이상이라는 기대감과 함께, 로슈를 뛰어넘는 초대형 블록버스터 신약이 될 것이라는 전망이 제기되며 긍정적인 분위기가 형성되고 있음.</t>
+          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암 신약', '매출']</t>
+          <t>['전선주', '박스권', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17930</v>
+        <v>12570</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.24%</t>
+          <t>'-3.38%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="E20" t="n">
-        <v>217</v>
+        <v>94</v>
       </c>
       <c r="F20" t="n">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="G20" t="n">
-        <v>1226</v>
+        <v>264</v>
       </c>
       <c r="H20" t="n">
-        <v>4.92</v>
+        <v>1.42</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,60 +2251,60 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>18530</v>
+        <v>13010</v>
       </c>
       <c r="K20" t="n">
-        <v>18950</v>
+        <v>12330</v>
       </c>
       <c r="L20" t="n">
-        <v>19870</v>
+        <v>13560</v>
       </c>
       <c r="M20" t="n">
-        <v>17840</v>
+        <v>12220</v>
       </c>
       <c r="N20" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>292194908030</v>
+        <v>50865146530</v>
       </c>
       <c r="P20" t="n">
-        <v>31500</v>
+        <v>22250</v>
       </c>
       <c r="Q20" t="n">
-        <v>1272</v>
+        <v>6000</v>
       </c>
       <c r="R20" t="n">
-        <v>-479000</v>
+        <v>-152000</v>
       </c>
       <c r="S20" t="n">
-        <v>6000</v>
+        <v>16000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 관련 언급. 5만원 목표가 제시 및 외인 대량 매도세 포착.</t>
+          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['광통신', '젠슨황', '외인매도']</t>
+          <t>['유증', '신주상장', '자사주매집']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29850</v>
+        <v>29800</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.98%</t>
+          <t>'-6.14%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F21" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G21" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H21" t="n">
         <v>10.78</v>
@@ -2358,7 +2358,7 @@
         <v>10.77</v>
       </c>
       <c r="O21" t="n">
-        <v>112400301825</v>
+        <v>114919206425</v>
       </c>
       <c r="P21" t="n">
         <v>75900</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>가온전선과의 비교에서 실력 및 기술력 차이 언급. 52주 고점 대비 큰 폭 하락 및 개인 매수세 지적. 외인 매도 물량 확인.</t>
+          <t>경쟁사 가온전선과의 주가 비교 언급과 함께 큰 폭의 하락세를 보이며 부정적인 전망과 투매 현상이 나타나고 있음. 객관적인 근거 제시 미흡.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['고점대비', '실력차이', '외인매도']</t>
+          <t>['대한전선', '가온전선', '하락']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12460</v>
+        <v>12450</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.18%</t>
+          <t>'-9.26%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.43</v>
       </c>
       <c r="E22" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F22" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G22" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H22" t="n">
         <v>2.04</v>
@@ -2450,7 +2450,7 @@
         <v>2.47</v>
       </c>
       <c r="O22" t="n">
-        <v>61106296705</v>
+        <v>61203543655</v>
       </c>
       <c r="P22" t="n">
         <v>39600</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>우주항공 테마의 변동성이 큰 가운데, 위성 발사 성공 소식에도 불구하고 재료 소멸 및 매도세로 인한 급락이 이어지며 투자자들의 불만이 고조되고 있음.</t>
+          <t>큐브 위성 발사 관련 기대감과 재료 소멸에 대한 우려가 공존하며, 테마 종목으로서의 변동성이 크고 단기적인 시세 차익에 대한 언급이 많음. 객관적 팩트 제시 부족.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['우주항공', '테마', '재료 소멸']</t>
+          <t>['켄코아에어로스페이스', '큐브위성', '우주항공']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20261007_15.xlsx
+++ b/data/trending_integrated_20261007_15.xlsx
@@ -578,13 +578,13 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F2" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H2" t="n">
         <v>3.27</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26477775894</v>
+        <v>26479689654</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -670,13 +670,13 @@
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F3" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G3" t="n">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="H3" t="n">
         <v>5.12</v>
@@ -702,7 +702,7 @@
         <v>5.14</v>
       </c>
       <c r="O3" t="n">
-        <v>143870503015</v>
+        <v>143914341935</v>
       </c>
       <c r="P3" t="n">
         <v>23500</v>
@@ -762,10 +762,10 @@
         <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
         <v>127</v>
@@ -794,7 +794,7 @@
         <v>1.31</v>
       </c>
       <c r="O4" t="n">
-        <v>41630078075</v>
+        <v>41648180025</v>
       </c>
       <c r="P4" t="n">
         <v>6000</v>
@@ -854,13 +854,13 @@
         <v>0.17</v>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F5" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G5" t="n">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="H5" t="n">
         <v>5.01</v>
@@ -886,7 +886,7 @@
         <v>4.84</v>
       </c>
       <c r="O5" t="n">
-        <v>33031909740</v>
+        <v>33032614380</v>
       </c>
       <c r="P5" t="n">
         <v>15900</v>
@@ -946,13 +946,13 @@
         <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H6" t="n">
         <v>2.82</v>
@@ -978,7 +978,7 @@
         <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>106259052175</v>
+        <v>106296797575</v>
       </c>
       <c r="P6" t="n">
         <v>30100</v>
@@ -1038,13 +1038,13 @@
         <v>0.98</v>
       </c>
       <c r="E7" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F7" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G7" t="n">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="H7" t="n">
         <v>2.37</v>
@@ -1070,7 +1070,7 @@
         <v>1.39</v>
       </c>
       <c r="O7" t="n">
-        <v>295688609380</v>
+        <v>295728345760</v>
       </c>
       <c r="P7" t="n">
         <v>17590</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>개인정보 유출 이슈와 함께 미국 보안주 상승, 양자보안 공급 논의 등 긍정적인 뉴스 및 기술적 분석 언급. 보안 이슈 부각 및 주포 움직임에 대한 기대감 존재.</t>
+          <t>양자보안 기술력 부각 및 10곳 이상 공급 논의, 보안 이슈 속에서 긍정적 모멘텀 형성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['라온시큐어', '양자보안', '해킹']</t>
+          <t>['양자보안', '공급 논의', '해킹']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F8" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G8" t="n">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="H8" t="n">
         <v>0.79</v>
@@ -1162,7 +1162,7 @@
         <v>0.48</v>
       </c>
       <c r="O8" t="n">
-        <v>231815029235</v>
+        <v>231858645115</v>
       </c>
       <c r="P8" t="n">
         <v>20850</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>한화파워향 가스터빈 블레이드 첫 납품 공시가 있었으나, 주가 부양보다는 개미 물량 확보에 집중하는 듯한 움직임을 보이며 긍정적/부정적 의견이 혼재.</t>
+          <t>가스터빈 블레이드 첫 납품 뉴스 기반 상승 기대, 차익 실현 매물 출회 가능성도 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['삼미금속', '가스터빈', '납품']</t>
+          <t>['가스터빈', '납품', '원전']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1254,7 +1254,7 @@
         <v>1.11</v>
       </c>
       <c r="O9" t="n">
-        <v>15648564668</v>
+        <v>15650173058</v>
       </c>
       <c r="P9" t="n">
         <v>4760</v>
@@ -1314,13 +1314,13 @@
         <v>3.32</v>
       </c>
       <c r="E10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F10" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G10" t="n">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="H10" t="n">
         <v>4.72</v>
@@ -1346,7 +1346,7 @@
         <v>1.4</v>
       </c>
       <c r="O10" t="n">
-        <v>245726776710</v>
+        <v>245772405890</v>
       </c>
       <c r="P10" t="n">
         <v>8100</v>
@@ -1409,10 +1409,10 @@
         <v>95</v>
       </c>
       <c r="F11" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="H11" t="n">
         <v>1.1</v>
@@ -1438,7 +1438,7 @@
         <v>1.87</v>
       </c>
       <c r="O11" t="n">
-        <v>74222883615</v>
+        <v>74235430665</v>
       </c>
       <c r="P11" t="n">
         <v>11370</v>
@@ -1498,13 +1498,13 @@
         <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="F12" t="n">
         <v>128</v>
       </c>
       <c r="G12" t="n">
-        <v>1298</v>
+        <v>1328</v>
       </c>
       <c r="H12" t="n">
         <v>4.12</v>
@@ -1530,7 +1530,7 @@
         <v>4.08</v>
       </c>
       <c r="O12" t="n">
-        <v>107346123250</v>
+        <v>107346364250</v>
       </c>
       <c r="P12" t="n">
         <v>1233000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>아일리아, 경구용 인슐린 관련 기대감이 높으며, 릴레이 계약 공시 및 외국인 수급에 대한 긍정적인 전망이 제시됨. 거래량 동반 시 상승 기대감 존재.</t>
+          <t>릴레이 계약 공시 기대감 속 외국인 공매도 숏커버링 관찰, 경구용 인슐린 L/O 예상.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['삼천당제약', '아일리아', '경구용 인슐린']</t>
+          <t>['릴레이 계약', '공매도 숏커버링', '경구용 인슐린']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1590,13 +1590,13 @@
         <v>0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F13" t="n">
         <v>181</v>
       </c>
       <c r="G13" t="n">
-        <v>917</v>
+        <v>931</v>
       </c>
       <c r="H13" t="n">
         <v>22.59</v>
@@ -1622,7 +1622,7 @@
         <v>22.56</v>
       </c>
       <c r="O13" t="n">
-        <v>178558868000</v>
+        <v>178573116500</v>
       </c>
       <c r="P13" t="n">
         <v>139200</v>
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="G14" t="n">
-        <v>1324</v>
+        <v>1402</v>
       </c>
       <c r="H14" t="n">
         <v>46.37</v>
@@ -1714,7 +1714,7 @@
         <v>46.41</v>
       </c>
       <c r="O14" t="n">
-        <v>4347472909500</v>
+        <v>4351285072500</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1726,11 +1726,11 @@
         <v>1548000</v>
       </c>
       <c r="S14" t="n">
-        <v>-319000</v>
+        <v>-531000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>AMD CEO의 HBM 대량 주문 및 파운드리 계약 소식에도 불구하고, 정치적 발언과 개인적인 비난이 주를 이루며 객관적인 사실 기반의 분석은 부족함.</t>
+          <t>HBM 대량 주문 및 파운드리 계약 가능성 언급, 그러나 정치적 언급으로 인해 투자 심리 혼조.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['HBM', '파운드리', 'AMD']</t>
+          <t>['HBM', '파운드리', '실적']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="H15" t="n">
         <v>9.5</v>
@@ -1806,7 +1806,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>61184533210</v>
+        <v>61199705710</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="G16" t="n">
-        <v>1852</v>
+        <v>1889</v>
       </c>
       <c r="H16" t="n">
         <v>49.71</v>
@@ -1898,7 +1898,7 @@
         <v>49.76</v>
       </c>
       <c r="O16" t="n">
-        <v>4388098496000</v>
+        <v>4388112280000</v>
       </c>
       <c r="P16" t="n">
         <v>2987000</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>나스닥 하락, 외인 매도세, 추세선 이탈 등 부정적인 요인과 함께 향후 주가 하락을 예견하는 의견이 많음. 객관적 근거는 일부 있으나 부정적 전망이 우세.</t>
+          <t>추세선 하향 돌파 및 기관 매도세 관찰, 외국인 매도와 환율 급락으로 인한 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '외인매도', '추세선']</t>
+          <t>['추세선', '기관 매도', '환율']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1964,7 +1964,7 @@
         <v>207</v>
       </c>
       <c r="G17" t="n">
-        <v>2505</v>
+        <v>2513</v>
       </c>
       <c r="H17" t="n">
         <v>14.12</v>
@@ -1990,7 +1990,7 @@
         <v>14.1</v>
       </c>
       <c r="O17" t="n">
-        <v>47317266050</v>
+        <v>47317770950</v>
       </c>
       <c r="P17" t="n">
         <v>69200</v>
@@ -2050,13 +2050,13 @@
         <v>1.11</v>
       </c>
       <c r="E18" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F18" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G18" t="n">
-        <v>1246</v>
+        <v>1271</v>
       </c>
       <c r="H18" t="n">
         <v>4.92</v>
@@ -2082,7 +2082,7 @@
         <v>3.81</v>
       </c>
       <c r="O18" t="n">
-        <v>292916741870</v>
+        <v>292952227190</v>
       </c>
       <c r="P18" t="n">
         <v>31500</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 관련 언급. 5만원 목표가 제시 및 외인 대량 매도세 포착.</t>
+          <t>미국 광통신 주가 상승 및 젠슨황의 광통신 지지 언급, 5만원 목표 달성 가능성 제시.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', '젠슨황', '외인매도']</t>
+          <t>['광통신', '젠슨황', '신고가']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,13 +2142,13 @@
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H19" t="n">
         <v>3.18</v>
@@ -2174,7 +2174,7 @@
         <v>3.12</v>
       </c>
       <c r="O19" t="n">
-        <v>29215985880</v>
+        <v>29219689580</v>
       </c>
       <c r="P19" t="n">
         <v>20300</v>
@@ -2234,13 +2234,13 @@
         <v>1.88</v>
       </c>
       <c r="E20" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F20" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G20" t="n">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="H20" t="n">
         <v>1.42</v>
@@ -2326,13 +2326,13 @@
         <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G21" t="n">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="H21" t="n">
         <v>10.78</v>
@@ -2358,7 +2358,7 @@
         <v>10.77</v>
       </c>
       <c r="O21" t="n">
-        <v>114919206425</v>
+        <v>115008040225</v>
       </c>
       <c r="P21" t="n">
         <v>75900</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>경쟁사 가온전선과의 주가 비교 언급과 함께 큰 폭의 하락세를 보이며 부정적인 전망과 투매 현상이 나타나고 있음. 객관적인 근거 제시 미흡.</t>
+          <t>주가 급락 및 외국인 대량 매도 관찰, 과거 대비 부진한 성과에 대한 투자자 불만 고조.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['대한전선', '가온전선', '하락']</t>
+          <t>['급락', '외국인 매도', '성과']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2418,13 +2418,13 @@
         <v>-0.43</v>
       </c>
       <c r="E22" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F22" t="n">
         <v>71</v>
       </c>
       <c r="G22" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="H22" t="n">
         <v>2.04</v>
@@ -2450,7 +2450,7 @@
         <v>2.47</v>
       </c>
       <c r="O22" t="n">
-        <v>61203543655</v>
+        <v>61208884705</v>
       </c>
       <c r="P22" t="n">
         <v>39600</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>큐브 위성 발사 관련 기대감과 재료 소멸에 대한 우려가 공존하며, 테마 종목으로서의 변동성이 크고 단기적인 시세 차익에 대한 언급이 많음. 객관적 팩트 제시 부족.</t>
+          <t>우주 테마 부각 및 공매도 관련 논쟁, 단기적인 변동성 후 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['켄코아에어로스페이스', '큐브위성', '우주항공']</t>
+          <t>['우주', '공매도', '위성']</t>
         </is>
       </c>
       <c r="X22" t="n">
